--- a/data/faturamento_realizado.xlsx
+++ b/data/faturamento_realizado.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1128"/>
+  <dimension ref="A1:D1129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1603,7 +1603,7 @@
         <v>629</v>
       </c>
       <c r="D73" t="n">
-        <v>211704.62</v>
+        <v>214193.82</v>
       </c>
     </row>
     <row r="74">
@@ -1843,7 +1843,7 @@
         <v>1116</v>
       </c>
       <c r="D88" t="n">
-        <v>76364.14999999999</v>
+        <v>78201.7</v>
       </c>
     </row>
     <row r="89">
@@ -3840,10 +3840,10 @@
         <v>46235</v>
       </c>
       <c r="C213" t="n">
-        <v>2562</v>
+        <v>2574</v>
       </c>
       <c r="D213" t="n">
-        <v>8096.6</v>
+        <v>23011.25</v>
       </c>
     </row>
     <row r="214">
@@ -3856,10 +3856,10 @@
         <v>46235</v>
       </c>
       <c r="C214" t="n">
-        <v>2574</v>
+        <v>2562</v>
       </c>
       <c r="D214" t="n">
-        <v>23011.25</v>
+        <v>8096.6</v>
       </c>
     </row>
     <row r="215">
@@ -4099,7 +4099,7 @@
         <v>2163</v>
       </c>
       <c r="D229" t="n">
-        <v>85920.42</v>
+        <v>88509.60000000001</v>
       </c>
     </row>
     <row r="230">
@@ -4659,7 +4659,7 @@
         <v>6</v>
       </c>
       <c r="D264" t="n">
-        <v>25401.46</v>
+        <v>33144.52</v>
       </c>
     </row>
     <row r="265">
@@ -4675,7 +4675,7 @@
         <v>530</v>
       </c>
       <c r="D265" t="n">
-        <v>15226.84</v>
+        <v>16855.61</v>
       </c>
     </row>
     <row r="266">
@@ -6403,7 +6403,7 @@
         <v>663</v>
       </c>
       <c r="D373" t="n">
-        <v>59695.69</v>
+        <v>60900.97</v>
       </c>
     </row>
     <row r="374">
@@ -8275,7 +8275,7 @@
         <v>2250</v>
       </c>
       <c r="D490" t="n">
-        <v>125312.45</v>
+        <v>131739.03</v>
       </c>
     </row>
     <row r="491">
@@ -8291,7 +8291,7 @@
         <v>89</v>
       </c>
       <c r="D491" t="n">
-        <v>188797.43</v>
+        <v>194844.09</v>
       </c>
     </row>
     <row r="492">
@@ -8323,7 +8323,7 @@
         <v>1063</v>
       </c>
       <c r="D493" t="n">
-        <v>141839.57</v>
+        <v>145042.8</v>
       </c>
     </row>
     <row r="494">
@@ -10547,7 +10547,7 @@
         <v>42</v>
       </c>
       <c r="D632" t="n">
-        <v>425510.63</v>
+        <v>435426.76</v>
       </c>
     </row>
     <row r="633">
@@ -10563,7 +10563,7 @@
         <v>2651</v>
       </c>
       <c r="D633" t="n">
-        <v>34958.28</v>
+        <v>35312.63</v>
       </c>
     </row>
     <row r="634">
@@ -10659,7 +10659,7 @@
         <v>854</v>
       </c>
       <c r="D639" t="n">
-        <v>112193.13</v>
+        <v>112938.92</v>
       </c>
     </row>
     <row r="640">
@@ -12595,7 +12595,7 @@
         <v>451</v>
       </c>
       <c r="D760" t="n">
-        <v>86607.53</v>
+        <v>88964.03999999999</v>
       </c>
     </row>
     <row r="761">
@@ -12611,7 +12611,7 @@
         <v>326</v>
       </c>
       <c r="D761" t="n">
-        <v>20401.1</v>
+        <v>20912.06</v>
       </c>
     </row>
     <row r="762">
@@ -12835,7 +12835,7 @@
         <v>818</v>
       </c>
       <c r="D775" t="n">
-        <v>190518</v>
+        <v>362491.8</v>
       </c>
     </row>
     <row r="776">
@@ -13091,7 +13091,7 @@
         <v>2558</v>
       </c>
       <c r="D791" t="n">
-        <v>9208.700000000001</v>
+        <v>9146.4</v>
       </c>
     </row>
     <row r="792">
@@ -13123,7 +13123,7 @@
         <v>2635</v>
       </c>
       <c r="D793" t="n">
-        <v>27827.23</v>
+        <v>76166.00999999999</v>
       </c>
     </row>
     <row r="794">
@@ -13721,49 +13721,49 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B831" s="2" t="n">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="C831" t="n">
-        <v>2250</v>
+        <v>2090</v>
       </c>
       <c r="D831" t="n">
-        <v>344749.01</v>
+        <v>-468.24</v>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B832" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C832" t="n">
-        <v>1632</v>
+        <v>2250</v>
       </c>
       <c r="D832" t="n">
-        <v>269195.14</v>
+        <v>344749.01</v>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B833" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C833" t="n">
-        <v>14</v>
+        <v>1632</v>
       </c>
       <c r="D833" t="n">
-        <v>398717.81</v>
+        <v>269195.14</v>
       </c>
     </row>
     <row r="834">
@@ -13776,26 +13776,26 @@
         <v>46204</v>
       </c>
       <c r="C834" t="n">
-        <v>2124</v>
+        <v>14</v>
       </c>
       <c r="D834" t="n">
-        <v>246730.75</v>
+        <v>398717.81</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B835" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C835" t="n">
-        <v>2789</v>
+        <v>2124</v>
       </c>
       <c r="D835" t="n">
-        <v>184511.68</v>
+        <v>246730.75</v>
       </c>
     </row>
     <row r="836">
@@ -13808,122 +13808,122 @@
         <v>46204</v>
       </c>
       <c r="C836" t="n">
-        <v>2631</v>
+        <v>2789</v>
       </c>
       <c r="D836" t="n">
-        <v>24020.76</v>
+        <v>184511.68</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B837" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C837" t="n">
-        <v>104</v>
+        <v>2631</v>
       </c>
       <c r="D837" t="n">
-        <v>132882.32</v>
+        <v>24020.76</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B838" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C838" t="n">
-        <v>2472</v>
+        <v>104</v>
       </c>
       <c r="D838" t="n">
-        <v>33739.06</v>
+        <v>132882.32</v>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B839" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C839" t="n">
-        <v>1372</v>
+        <v>2472</v>
       </c>
       <c r="D839" t="n">
-        <v>183710.88</v>
+        <v>33739.06</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B840" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C840" t="n">
-        <v>2772</v>
+        <v>1372</v>
       </c>
       <c r="D840" t="n">
-        <v>40111</v>
+        <v>183710.88</v>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B841" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C841" t="n">
-        <v>1381</v>
+        <v>2772</v>
       </c>
       <c r="D841" t="n">
-        <v>269835.24</v>
+        <v>40111</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B842" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C842" t="n">
-        <v>1890</v>
+        <v>1381</v>
       </c>
       <c r="D842" t="n">
-        <v>373689.32</v>
+        <v>269835.24</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B843" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C843" t="n">
-        <v>451</v>
+        <v>1890</v>
       </c>
       <c r="D843" t="n">
-        <v>268444.6</v>
+        <v>373689.32</v>
       </c>
     </row>
     <row r="844">
@@ -13936,74 +13936,74 @@
         <v>46204</v>
       </c>
       <c r="C844" t="n">
-        <v>40</v>
+        <v>451</v>
       </c>
       <c r="D844" t="n">
-        <v>235955.26</v>
+        <v>268444.6</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B845" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C845" t="n">
-        <v>2490</v>
+        <v>40</v>
       </c>
       <c r="D845" t="n">
-        <v>28123.34</v>
+        <v>235955.26</v>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B846" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C846" t="n">
-        <v>2442</v>
+        <v>2490</v>
       </c>
       <c r="D846" t="n">
-        <v>67030.33</v>
+        <v>28123.34</v>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B847" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C847" t="n">
-        <v>2733</v>
+        <v>2442</v>
       </c>
       <c r="D847" t="n">
-        <v>4257.24</v>
+        <v>67030.33</v>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B848" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C848" t="n">
-        <v>6</v>
+        <v>2733</v>
       </c>
       <c r="D848" t="n">
-        <v>2171.24</v>
+        <v>4257.24</v>
       </c>
     </row>
     <row r="849">
@@ -14016,58 +14016,58 @@
         <v>46204</v>
       </c>
       <c r="C849" t="n">
-        <v>483</v>
+        <v>6</v>
       </c>
       <c r="D849" t="n">
-        <v>563758.96</v>
+        <v>2171.24</v>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B850" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C850" t="n">
-        <v>2118</v>
+        <v>483</v>
       </c>
       <c r="D850" t="n">
-        <v>25014.09</v>
+        <v>563758.96</v>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B851" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C851" t="n">
-        <v>2363</v>
+        <v>2118</v>
       </c>
       <c r="D851" t="n">
-        <v>158965.96</v>
+        <v>25014.09</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B852" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C852" t="n">
-        <v>2245</v>
+        <v>2363</v>
       </c>
       <c r="D852" t="n">
-        <v>162530.12</v>
+        <v>158965.96</v>
       </c>
     </row>
     <row r="853">
@@ -14080,90 +14080,90 @@
         <v>46204</v>
       </c>
       <c r="C853" t="n">
-        <v>1364</v>
+        <v>2245</v>
       </c>
       <c r="D853" t="n">
-        <v>12440.8</v>
+        <v>162530.12</v>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B854" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C854" t="n">
-        <v>2576</v>
+        <v>1364</v>
       </c>
       <c r="D854" t="n">
-        <v>16501.47</v>
+        <v>12440.8</v>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B855" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C855" t="n">
-        <v>2392</v>
+        <v>2576</v>
       </c>
       <c r="D855" t="n">
-        <v>182866.28</v>
+        <v>16501.47</v>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B856" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C856" t="n">
-        <v>2539</v>
+        <v>2392</v>
       </c>
       <c r="D856" t="n">
-        <v>21344.65</v>
+        <v>182866.28</v>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B857" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C857" t="n">
-        <v>2769</v>
+        <v>2539</v>
       </c>
       <c r="D857" t="n">
-        <v>159754.22</v>
+        <v>21344.65</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B858" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C858" t="n">
-        <v>2554</v>
+        <v>2769</v>
       </c>
       <c r="D858" t="n">
-        <v>15679.43</v>
+        <v>159754.22</v>
       </c>
     </row>
     <row r="859">
@@ -14176,42 +14176,42 @@
         <v>46204</v>
       </c>
       <c r="C859" t="n">
-        <v>2325</v>
+        <v>2554</v>
       </c>
       <c r="D859" t="n">
-        <v>118806.58</v>
+        <v>15679.43</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B860" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C860" t="n">
-        <v>1501</v>
+        <v>2325</v>
       </c>
       <c r="D860" t="n">
-        <v>74106.8</v>
+        <v>118806.58</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B861" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C861" t="n">
-        <v>2556</v>
+        <v>1501</v>
       </c>
       <c r="D861" t="n">
-        <v>21255.75</v>
+        <v>74106.8</v>
       </c>
     </row>
     <row r="862">
@@ -14224,42 +14224,42 @@
         <v>46204</v>
       </c>
       <c r="C862" t="n">
-        <v>2145</v>
+        <v>2556</v>
       </c>
       <c r="D862" t="n">
-        <v>63527.47</v>
+        <v>21255.75</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B863" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C863" t="n">
-        <v>703</v>
+        <v>2145</v>
       </c>
       <c r="D863" t="n">
-        <v>292695.16</v>
+        <v>63527.47</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B864" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C864" t="n">
-        <v>2567</v>
+        <v>703</v>
       </c>
       <c r="D864" t="n">
-        <v>79212.86</v>
+        <v>292695.16</v>
       </c>
     </row>
     <row r="865">
@@ -14272,10 +14272,10 @@
         <v>46204</v>
       </c>
       <c r="C865" t="n">
-        <v>2249</v>
+        <v>2567</v>
       </c>
       <c r="D865" t="n">
-        <v>196759</v>
+        <v>79212.86</v>
       </c>
     </row>
     <row r="866">
@@ -14288,74 +14288,74 @@
         <v>46204</v>
       </c>
       <c r="C866" t="n">
-        <v>2551</v>
+        <v>2249</v>
       </c>
       <c r="D866" t="n">
-        <v>31252.25</v>
+        <v>196759</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B867" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C867" t="n">
-        <v>2496</v>
+        <v>2551</v>
       </c>
       <c r="D867" t="n">
-        <v>205089.39</v>
+        <v>31252.25</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B868" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C868" t="n">
-        <v>326</v>
+        <v>2496</v>
       </c>
       <c r="D868" t="n">
-        <v>754.74</v>
+        <v>205089.39</v>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B869" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C869" t="n">
-        <v>816</v>
+        <v>326</v>
       </c>
       <c r="D869" t="n">
-        <v>193761.14</v>
+        <v>754.74</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B870" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C870" t="n">
-        <v>325</v>
+        <v>816</v>
       </c>
       <c r="D870" t="n">
-        <v>2193.42</v>
+        <v>193761.14</v>
       </c>
     </row>
     <row r="871">
@@ -14368,42 +14368,42 @@
         <v>46204</v>
       </c>
       <c r="C871" t="n">
-        <v>2741</v>
+        <v>325</v>
       </c>
       <c r="D871" t="n">
-        <v>2514.46</v>
+        <v>2193.42</v>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B872" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C872" t="n">
-        <v>2557</v>
+        <v>2741</v>
       </c>
       <c r="D872" t="n">
-        <v>35838.06</v>
+        <v>2514.46</v>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B873" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C873" t="n">
-        <v>326</v>
+        <v>2557</v>
       </c>
       <c r="D873" t="n">
-        <v>2489.81</v>
+        <v>35838.06</v>
       </c>
     </row>
     <row r="874">
@@ -14416,42 +14416,42 @@
         <v>46204</v>
       </c>
       <c r="C874" t="n">
-        <v>2114</v>
+        <v>326</v>
       </c>
       <c r="D874" t="n">
-        <v>138617.75</v>
+        <v>2489.81</v>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B875" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C875" t="n">
-        <v>2689</v>
+        <v>2114</v>
       </c>
       <c r="D875" t="n">
-        <v>36232.39</v>
+        <v>138617.75</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B876" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C876" t="n">
-        <v>2755</v>
+        <v>2689</v>
       </c>
       <c r="D876" t="n">
-        <v>18491.81</v>
+        <v>36232.39</v>
       </c>
     </row>
     <row r="877">
@@ -14464,26 +14464,26 @@
         <v>46204</v>
       </c>
       <c r="C877" t="n">
-        <v>374</v>
+        <v>2755</v>
       </c>
       <c r="D877" t="n">
-        <v>19985.99</v>
+        <v>18491.81</v>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B878" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C878" t="n">
-        <v>2706</v>
+        <v>374</v>
       </c>
       <c r="D878" t="n">
-        <v>5134.89</v>
+        <v>19985.99</v>
       </c>
     </row>
     <row r="879">
@@ -14496,42 +14496,42 @@
         <v>46204</v>
       </c>
       <c r="C879" t="n">
-        <v>2584</v>
+        <v>2706</v>
       </c>
       <c r="D879" t="n">
-        <v>40851.53</v>
+        <v>5134.89</v>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B880" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C880" t="n">
-        <v>2433</v>
+        <v>2584</v>
       </c>
       <c r="D880" t="n">
-        <v>4223.19</v>
+        <v>40851.53</v>
       </c>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B881" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C881" t="n">
-        <v>2718</v>
+        <v>2433</v>
       </c>
       <c r="D881" t="n">
-        <v>62272.26</v>
+        <v>4223.19</v>
       </c>
     </row>
     <row r="882">
@@ -14544,74 +14544,74 @@
         <v>46204</v>
       </c>
       <c r="C882" t="n">
-        <v>6564</v>
+        <v>2718</v>
       </c>
       <c r="D882" t="n">
-        <v>63409.31</v>
+        <v>62272.26</v>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B883" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C883" t="n">
-        <v>2691</v>
+        <v>6564</v>
       </c>
       <c r="D883" t="n">
-        <v>170842.3</v>
+        <v>63409.31</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B884" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C884" t="n">
-        <v>2621</v>
+        <v>2691</v>
       </c>
       <c r="D884" t="n">
-        <v>59462.73</v>
+        <v>170842.3</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B885" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C885" t="n">
-        <v>2799</v>
+        <v>2621</v>
       </c>
       <c r="D885" t="n">
-        <v>22612.81</v>
+        <v>59462.73</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B886" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C886" t="n">
-        <v>2599</v>
+        <v>2799</v>
       </c>
       <c r="D886" t="n">
-        <v>11057.04</v>
+        <v>22612.81</v>
       </c>
     </row>
     <row r="887">
@@ -14624,10 +14624,10 @@
         <v>46204</v>
       </c>
       <c r="C887" t="n">
-        <v>2069</v>
+        <v>2599</v>
       </c>
       <c r="D887" t="n">
-        <v>1694.84</v>
+        <v>11057.04</v>
       </c>
     </row>
     <row r="888">
@@ -14640,282 +14640,282 @@
         <v>46204</v>
       </c>
       <c r="C888" t="n">
-        <v>1327</v>
+        <v>2069</v>
       </c>
       <c r="D888" t="n">
-        <v>12045.27</v>
+        <v>1694.84</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B889" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C889" t="n">
-        <v>2201</v>
+        <v>1327</v>
       </c>
       <c r="D889" t="n">
-        <v>1867.57</v>
+        <v>12045.27</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B890" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C890" t="n">
-        <v>1076</v>
+        <v>2201</v>
       </c>
       <c r="D890" t="n">
-        <v>4759.26</v>
+        <v>1867.57</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B891" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C891" t="n">
-        <v>2133</v>
+        <v>1076</v>
       </c>
       <c r="D891" t="n">
-        <v>1383.1</v>
+        <v>4759.26</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B892" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C892" t="n">
-        <v>530</v>
+        <v>2133</v>
       </c>
       <c r="D892" t="n">
-        <v>0</v>
+        <v>1383.1</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B893" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C893" t="n">
-        <v>2727</v>
+        <v>530</v>
       </c>
       <c r="D893" t="n">
-        <v>23136.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B894" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C894" t="n">
-        <v>2463</v>
+        <v>2727</v>
       </c>
       <c r="D894" t="n">
-        <v>0</v>
+        <v>23136.25</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B895" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C895" t="n">
-        <v>2721</v>
+        <v>2463</v>
       </c>
       <c r="D895" t="n">
-        <v>484.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B896" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C896" t="n">
-        <v>89</v>
+        <v>2721</v>
       </c>
       <c r="D896" t="n">
-        <v>924.8</v>
+        <v>484.09</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B897" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C897" t="n">
-        <v>716</v>
+        <v>89</v>
       </c>
       <c r="D897" t="n">
-        <v>30000</v>
+        <v>924.8</v>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B898" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C898" t="n">
-        <v>2433</v>
+        <v>716</v>
       </c>
       <c r="D898" t="n">
-        <v>302.4</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B899" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C899" t="n">
-        <v>2676</v>
+        <v>2433</v>
       </c>
       <c r="D899" t="n">
-        <v>8793.26</v>
+        <v>302.4</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B900" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C900" t="n">
-        <v>2687</v>
+        <v>2676</v>
       </c>
       <c r="D900" t="n">
-        <v>942.87</v>
+        <v>8793.26</v>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B901" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C901" t="n">
-        <v>636</v>
+        <v>2687</v>
       </c>
       <c r="D901" t="n">
-        <v>468.95</v>
+        <v>942.87</v>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B902" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C902" t="n">
-        <v>1289</v>
+        <v>636</v>
       </c>
       <c r="D902" t="n">
-        <v>397.4</v>
+        <v>468.95</v>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B903" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C903" t="n">
-        <v>1427</v>
+        <v>1289</v>
       </c>
       <c r="D903" t="n">
-        <v>1126.22</v>
+        <v>397.4</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B904" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C904" t="n">
-        <v>619</v>
+        <v>1427</v>
       </c>
       <c r="D904" t="n">
-        <v>346.8</v>
+        <v>1126.22</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B905" s="2" t="n">
-        <v>46235</v>
+        <v>46204</v>
       </c>
       <c r="C905" t="n">
-        <v>941</v>
+        <v>619</v>
       </c>
       <c r="D905" t="n">
-        <v>54797.05</v>
+        <v>346.8</v>
       </c>
     </row>
     <row r="906">
@@ -14928,10 +14928,10 @@
         <v>46235</v>
       </c>
       <c r="C906" t="n">
-        <v>2810</v>
+        <v>941</v>
       </c>
       <c r="D906" t="n">
-        <v>47437.14</v>
+        <v>54797.05</v>
       </c>
     </row>
     <row r="907">
@@ -14944,26 +14944,26 @@
         <v>46235</v>
       </c>
       <c r="C907" t="n">
-        <v>2726</v>
+        <v>2810</v>
       </c>
       <c r="D907" t="n">
-        <v>35432.85</v>
+        <v>47437.14</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B908" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C908" t="n">
-        <v>2652</v>
+        <v>2726</v>
       </c>
       <c r="D908" t="n">
-        <v>79807.24000000001</v>
+        <v>35432.85</v>
       </c>
     </row>
     <row r="909">
@@ -14976,90 +14976,90 @@
         <v>46235</v>
       </c>
       <c r="C909" t="n">
-        <v>2346</v>
+        <v>2652</v>
       </c>
       <c r="D909" t="n">
-        <v>29871.74</v>
+        <v>79807.24000000001</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B910" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C910" t="n">
-        <v>2716</v>
+        <v>2346</v>
       </c>
       <c r="D910" t="n">
-        <v>16695.61</v>
+        <v>29871.74</v>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B911" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C911" t="n">
-        <v>1518</v>
+        <v>2716</v>
       </c>
       <c r="D911" t="n">
-        <v>101108.25</v>
+        <v>16695.61</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B912" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C912" t="n">
-        <v>1064</v>
+        <v>1518</v>
       </c>
       <c r="D912" t="n">
-        <v>144199.97</v>
+        <v>101108.25</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B913" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C913" t="n">
-        <v>2648</v>
+        <v>1064</v>
       </c>
       <c r="D913" t="n">
-        <v>50946.45</v>
+        <v>144199.97</v>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B914" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C914" t="n">
-        <v>415</v>
+        <v>2648</v>
       </c>
       <c r="D914" t="n">
-        <v>202931.83</v>
+        <v>50946.45</v>
       </c>
     </row>
     <row r="915">
@@ -15072,10 +15072,10 @@
         <v>46235</v>
       </c>
       <c r="C915" t="n">
-        <v>104</v>
+        <v>415</v>
       </c>
       <c r="D915" t="n">
-        <v>47814.26</v>
+        <v>203587.76</v>
       </c>
     </row>
     <row r="916">
@@ -15088,26 +15088,26 @@
         <v>46235</v>
       </c>
       <c r="C916" t="n">
-        <v>1381</v>
+        <v>104</v>
       </c>
       <c r="D916" t="n">
-        <v>120368.39</v>
+        <v>47814.26</v>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B917" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C917" t="n">
-        <v>1810</v>
+        <v>1381</v>
       </c>
       <c r="D917" t="n">
-        <v>9309.870000000001</v>
+        <v>120368.39</v>
       </c>
     </row>
     <row r="918">
@@ -15120,74 +15120,74 @@
         <v>46235</v>
       </c>
       <c r="C918" t="n">
-        <v>610</v>
+        <v>1810</v>
       </c>
       <c r="D918" t="n">
-        <v>396350.11</v>
+        <v>13596.67</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B919" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C919" t="n">
-        <v>2510</v>
+        <v>610</v>
       </c>
       <c r="D919" t="n">
-        <v>328377.21</v>
+        <v>400686.98</v>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B920" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C920" t="n">
-        <v>626</v>
+        <v>2510</v>
       </c>
       <c r="D920" t="n">
-        <v>631021.37</v>
+        <v>328377.21</v>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B921" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C921" t="n">
-        <v>2178</v>
+        <v>626</v>
       </c>
       <c r="D921" t="n">
-        <v>58636.54</v>
+        <v>631021.37</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B922" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C922" t="n">
-        <v>2365</v>
+        <v>2178</v>
       </c>
       <c r="D922" t="n">
-        <v>18834.34</v>
+        <v>58636.54</v>
       </c>
     </row>
     <row r="923">
@@ -15200,26 +15200,26 @@
         <v>46235</v>
       </c>
       <c r="C923" t="n">
-        <v>2146</v>
+        <v>2365</v>
       </c>
       <c r="D923" t="n">
-        <v>66901.72</v>
+        <v>18834.34</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B924" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C924" t="n">
-        <v>2363</v>
+        <v>2146</v>
       </c>
       <c r="D924" t="n">
-        <v>32854.18</v>
+        <v>66901.72</v>
       </c>
     </row>
     <row r="925">
@@ -15232,74 +15232,74 @@
         <v>46235</v>
       </c>
       <c r="C925" t="n">
-        <v>325</v>
+        <v>2363</v>
       </c>
       <c r="D925" t="n">
-        <v>4596.37</v>
+        <v>32854.18</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B926" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C926" t="n">
-        <v>1585</v>
+        <v>325</v>
       </c>
       <c r="D926" t="n">
-        <v>60055.76</v>
+        <v>4596.37</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B927" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C927" t="n">
-        <v>2251</v>
+        <v>1585</v>
       </c>
       <c r="D927" t="n">
-        <v>72349.09</v>
+        <v>60041.44</v>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B928" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C928" t="n">
-        <v>802</v>
+        <v>2251</v>
       </c>
       <c r="D928" t="n">
-        <v>23131.4</v>
+        <v>72349.09</v>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B929" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C929" t="n">
-        <v>2496</v>
+        <v>802</v>
       </c>
       <c r="D929" t="n">
-        <v>60509.77</v>
+        <v>23131.4</v>
       </c>
     </row>
     <row r="930">
@@ -15312,10 +15312,10 @@
         <v>46235</v>
       </c>
       <c r="C930" t="n">
-        <v>2758</v>
+        <v>2496</v>
       </c>
       <c r="D930" t="n">
-        <v>9279.52</v>
+        <v>60509.77</v>
       </c>
     </row>
     <row r="931">
@@ -15328,26 +15328,26 @@
         <v>46235</v>
       </c>
       <c r="C931" t="n">
-        <v>2494</v>
+        <v>2758</v>
       </c>
       <c r="D931" t="n">
-        <v>70187.03999999999</v>
+        <v>9279.52</v>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B932" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C932" t="n">
-        <v>2394</v>
+        <v>2494</v>
       </c>
       <c r="D932" t="n">
-        <v>15472.44</v>
+        <v>70187.03999999999</v>
       </c>
     </row>
     <row r="933">
@@ -15360,10 +15360,10 @@
         <v>46235</v>
       </c>
       <c r="C933" t="n">
-        <v>2551</v>
+        <v>2394</v>
       </c>
       <c r="D933" t="n">
-        <v>6208.1</v>
+        <v>15472.44</v>
       </c>
     </row>
     <row r="934">
@@ -15376,106 +15376,106 @@
         <v>46235</v>
       </c>
       <c r="C934" t="n">
-        <v>2249</v>
+        <v>2551</v>
       </c>
       <c r="D934" t="n">
-        <v>95424.94</v>
+        <v>6208.1</v>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B935" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C935" t="n">
-        <v>1324</v>
+        <v>2249</v>
       </c>
       <c r="D935" t="n">
-        <v>122844.29</v>
+        <v>95424.94</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B936" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C936" t="n">
-        <v>2765</v>
+        <v>1324</v>
       </c>
       <c r="D936" t="n">
-        <v>18128.81</v>
+        <v>122844.29</v>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B937" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C937" t="n">
-        <v>2015</v>
+        <v>2765</v>
       </c>
       <c r="D937" t="n">
-        <v>730.95</v>
+        <v>18128.81</v>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B938" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C938" t="n">
-        <v>2790</v>
+        <v>2015</v>
       </c>
       <c r="D938" t="n">
-        <v>3619.28</v>
+        <v>730.95</v>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B939" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C939" t="n">
-        <v>325</v>
+        <v>2790</v>
       </c>
       <c r="D939" t="n">
-        <v>837.7</v>
+        <v>3619.28</v>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B940" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C940" t="n">
-        <v>716</v>
+        <v>325</v>
       </c>
       <c r="D940" t="n">
-        <v>30000</v>
+        <v>837.7</v>
       </c>
     </row>
     <row r="941">
@@ -15488,186 +15488,186 @@
         <v>46235</v>
       </c>
       <c r="C941" t="n">
-        <v>326</v>
+        <v>716</v>
       </c>
       <c r="D941" t="n">
-        <v>106800</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B942" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C942" t="n">
-        <v>1907</v>
+        <v>326</v>
       </c>
       <c r="D942" t="n">
-        <v>179899.97</v>
+        <v>106800</v>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B943" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C943" t="n">
-        <v>2763</v>
+        <v>1907</v>
       </c>
       <c r="D943" t="n">
-        <v>1279.37</v>
+        <v>179899.97</v>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B944" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C944" t="n">
-        <v>2724</v>
+        <v>2763</v>
       </c>
       <c r="D944" t="n">
-        <v>1537.11</v>
+        <v>1279.37</v>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B945" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C945" t="n">
-        <v>33</v>
+        <v>2724</v>
       </c>
       <c r="D945" t="n">
-        <v>4704.37</v>
+        <v>1537.11</v>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B946" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C946" t="n">
-        <v>2802</v>
+        <v>33</v>
       </c>
       <c r="D946" t="n">
-        <v>21797.87</v>
+        <v>4704.37</v>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B947" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C947" t="n">
-        <v>2463</v>
+        <v>2802</v>
       </c>
       <c r="D947" t="n">
-        <v>49662.73</v>
+        <v>21797.87</v>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B948" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C948" t="n">
-        <v>2549</v>
+        <v>2463</v>
       </c>
       <c r="D948" t="n">
-        <v>1475.52</v>
+        <v>49662.73</v>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B949" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C949" t="n">
-        <v>1254</v>
+        <v>2549</v>
       </c>
       <c r="D949" t="n">
-        <v>139724.16</v>
+        <v>1475.52</v>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B950" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C950" t="n">
-        <v>2745</v>
+        <v>1254</v>
       </c>
       <c r="D950" t="n">
-        <v>92314.88</v>
+        <v>139724.16</v>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B951" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C951" t="n">
-        <v>2547</v>
+        <v>2745</v>
       </c>
       <c r="D951" t="n">
-        <v>12669.51</v>
+        <v>92314.88</v>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B952" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C952" t="n">
-        <v>2744</v>
+        <v>2547</v>
       </c>
       <c r="D952" t="n">
-        <v>18998.78</v>
+        <v>12669.51</v>
       </c>
     </row>
     <row r="953">
@@ -15680,10 +15680,10 @@
         <v>46235</v>
       </c>
       <c r="C953" t="n">
-        <v>2772</v>
+        <v>2744</v>
       </c>
       <c r="D953" t="n">
-        <v>21458</v>
+        <v>18998.78</v>
       </c>
     </row>
     <row r="954">
@@ -15696,74 +15696,74 @@
         <v>46235</v>
       </c>
       <c r="C954" t="n">
-        <v>2674</v>
+        <v>2772</v>
       </c>
       <c r="D954" t="n">
-        <v>131775.82</v>
+        <v>20712.21</v>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B955" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C955" t="n">
-        <v>2499</v>
+        <v>2674</v>
       </c>
       <c r="D955" t="n">
-        <v>4768.44</v>
+        <v>131775.82</v>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B956" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C956" t="n">
-        <v>2698</v>
+        <v>2499</v>
       </c>
       <c r="D956" t="n">
-        <v>7522.14</v>
+        <v>4768.44</v>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B957" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C957" t="n">
-        <v>2178</v>
+        <v>2698</v>
       </c>
       <c r="D957" t="n">
-        <v>2354.98</v>
+        <v>7522.14</v>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B958" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C958" t="n">
-        <v>2069</v>
+        <v>2178</v>
       </c>
       <c r="D958" t="n">
-        <v>72676.5</v>
+        <v>2354.98</v>
       </c>
     </row>
     <row r="959">
@@ -15776,154 +15776,154 @@
         <v>46235</v>
       </c>
       <c r="C959" t="n">
-        <v>1277</v>
+        <v>2069</v>
       </c>
       <c r="D959" t="n">
-        <v>59697.71</v>
+        <v>72676.5</v>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B960" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C960" t="n">
-        <v>2667</v>
+        <v>1277</v>
       </c>
       <c r="D960" t="n">
-        <v>8388.709999999999</v>
+        <v>59697.71</v>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B961" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C961" t="n">
-        <v>2197</v>
+        <v>2667</v>
       </c>
       <c r="D961" t="n">
-        <v>1005.67</v>
+        <v>8388.709999999999</v>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B962" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C962" t="n">
-        <v>2498</v>
+        <v>2197</v>
       </c>
       <c r="D962" t="n">
-        <v>10096.56</v>
+        <v>1005.67</v>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B963" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C963" t="n">
-        <v>2566</v>
+        <v>2498</v>
       </c>
       <c r="D963" t="n">
-        <v>30695.32</v>
+        <v>10096.56</v>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B964" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C964" t="n">
-        <v>1075</v>
+        <v>2566</v>
       </c>
       <c r="D964" t="n">
-        <v>688.1799999999999</v>
+        <v>30695.32</v>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B965" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C965" t="n">
-        <v>2402</v>
+        <v>1075</v>
       </c>
       <c r="D965" t="n">
-        <v>86381.7</v>
+        <v>688.1799999999999</v>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B966" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C966" t="n">
-        <v>2817</v>
+        <v>2402</v>
       </c>
       <c r="D966" t="n">
-        <v>33364.45</v>
+        <v>86381.7</v>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B967" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C967" t="n">
-        <v>2577</v>
+        <v>2817</v>
       </c>
       <c r="D967" t="n">
-        <v>91951.78</v>
+        <v>33364.45</v>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B968" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C968" t="n">
-        <v>2607</v>
+        <v>2577</v>
       </c>
       <c r="D968" t="n">
-        <v>14899.43</v>
+        <v>91951.78</v>
       </c>
     </row>
     <row r="969">
@@ -15936,330 +15936,330 @@
         <v>46235</v>
       </c>
       <c r="C969" t="n">
-        <v>2580</v>
+        <v>2607</v>
       </c>
       <c r="D969" t="n">
-        <v>1512.68</v>
+        <v>14899.43</v>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B970" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C970" t="n">
-        <v>716</v>
+        <v>2580</v>
       </c>
       <c r="D970" t="n">
-        <v>27151.72</v>
+        <v>1512.68</v>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B971" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C971" t="n">
-        <v>2691</v>
+        <v>716</v>
       </c>
       <c r="D971" t="n">
-        <v>-29642.95</v>
+        <v>27151.72</v>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B972" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C972" t="n">
-        <v>783</v>
+        <v>2691</v>
       </c>
       <c r="D972" t="n">
-        <v>18781.03</v>
+        <v>-29642.95</v>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B973" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C973" t="n">
-        <v>2539</v>
+        <v>783</v>
       </c>
       <c r="D973" t="n">
-        <v>767.84</v>
+        <v>18781.03</v>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B974" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C974" t="n">
-        <v>2692</v>
+        <v>2539</v>
       </c>
       <c r="D974" t="n">
-        <v>4279.32</v>
+        <v>767.84</v>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B975" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C975" t="n">
-        <v>2114</v>
+        <v>2692</v>
       </c>
       <c r="D975" t="n">
-        <v>14453.44</v>
+        <v>4279.32</v>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B976" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C976" t="n">
-        <v>2727</v>
+        <v>2114</v>
       </c>
       <c r="D976" t="n">
-        <v>2818.28</v>
+        <v>14453.44</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B977" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C977" t="n">
-        <v>1478</v>
+        <v>2727</v>
       </c>
       <c r="D977" t="n">
-        <v>587.88</v>
+        <v>2818.28</v>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B978" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C978" t="n">
-        <v>400</v>
+        <v>1478</v>
       </c>
       <c r="D978" t="n">
-        <v>1284.2</v>
+        <v>587.88</v>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B979" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C979" t="n">
-        <v>2279</v>
+        <v>400</v>
       </c>
       <c r="D979" t="n">
-        <v>871.97</v>
+        <v>1284.2</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B980" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C980" t="n">
-        <v>2813</v>
+        <v>2279</v>
       </c>
       <c r="D980" t="n">
-        <v>3987.05</v>
+        <v>871.97</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B981" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C981" t="n">
-        <v>2821</v>
+        <v>2813</v>
       </c>
       <c r="D981" t="n">
-        <v>6153.81</v>
+        <v>3987.05</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B982" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C982" t="n">
-        <v>2732</v>
+        <v>2821</v>
       </c>
       <c r="D982" t="n">
-        <v>-519.77</v>
+        <v>6153.81</v>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B983" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C983" t="n">
-        <v>2561</v>
+        <v>2732</v>
       </c>
       <c r="D983" t="n">
-        <v>811.97</v>
+        <v>-519.77</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B984" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C984" t="n">
-        <v>2741</v>
+        <v>2561</v>
       </c>
       <c r="D984" t="n">
-        <v>423</v>
+        <v>811.97</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B985" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C985" t="n">
-        <v>947</v>
+        <v>2741</v>
       </c>
       <c r="D985" t="n">
-        <v>3783.08</v>
+        <v>423</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B986" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C986" t="n">
-        <v>2822</v>
+        <v>947</v>
       </c>
       <c r="D986" t="n">
-        <v>4814.28</v>
+        <v>3783.08</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B987" s="2" t="n">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="C987" t="n">
-        <v>1993</v>
+        <v>2822</v>
       </c>
       <c r="D987" t="n">
-        <v>301886.75</v>
+        <v>4814.28</v>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B988" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C988" t="n">
-        <v>609</v>
+        <v>1993</v>
       </c>
       <c r="D988" t="n">
-        <v>232782.47</v>
+        <v>301886.75</v>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B989" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C989" t="n">
-        <v>1340</v>
+        <v>609</v>
       </c>
       <c r="D989" t="n">
-        <v>90029.28999999999</v>
+        <v>232782.47</v>
       </c>
     </row>
     <row r="990">
@@ -16272,218 +16272,218 @@
         <v>46204</v>
       </c>
       <c r="C990" t="n">
-        <v>781</v>
+        <v>1340</v>
       </c>
       <c r="D990" t="n">
-        <v>77506.66</v>
+        <v>90029.28999999999</v>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B991" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C991" t="n">
-        <v>1259</v>
+        <v>781</v>
       </c>
       <c r="D991" t="n">
-        <v>267045.89</v>
+        <v>77506.66</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B992" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C992" t="n">
-        <v>2790</v>
+        <v>1259</v>
       </c>
       <c r="D992" t="n">
-        <v>33500.8</v>
+        <v>267045.89</v>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B993" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C993" t="n">
-        <v>2015</v>
+        <v>2790</v>
       </c>
       <c r="D993" t="n">
-        <v>342765.94</v>
+        <v>33500.8</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B994" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C994" t="n">
-        <v>132</v>
+        <v>2015</v>
       </c>
       <c r="D994" t="n">
-        <v>412327.36</v>
+        <v>342765.94</v>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B995" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C995" t="n">
-        <v>2607</v>
+        <v>132</v>
       </c>
       <c r="D995" t="n">
-        <v>7558.05</v>
+        <v>412327.36</v>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B996" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C996" t="n">
-        <v>2494</v>
+        <v>2607</v>
       </c>
       <c r="D996" t="n">
-        <v>169823.24</v>
+        <v>7558.05</v>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B997" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C997" t="n">
-        <v>20</v>
+        <v>2494</v>
       </c>
       <c r="D997" t="n">
-        <v>69688.86</v>
+        <v>169823.24</v>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B998" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C998" t="n">
-        <v>360</v>
+        <v>20</v>
       </c>
       <c r="D998" t="n">
-        <v>528964.37</v>
+        <v>69688.86</v>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B999" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C999" t="n">
-        <v>2089</v>
+        <v>360</v>
       </c>
       <c r="D999" t="n">
-        <v>88194.66</v>
+        <v>528964.37</v>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B1000" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1000" t="n">
-        <v>530</v>
+        <v>2089</v>
       </c>
       <c r="D1000" t="n">
-        <v>91388.41</v>
+        <v>88194.66</v>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B1001" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1001" t="n">
-        <v>1690</v>
+        <v>530</v>
       </c>
       <c r="D1001" t="n">
-        <v>13331.41</v>
+        <v>91388.41</v>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B1002" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1002" t="n">
-        <v>2722</v>
+        <v>1690</v>
       </c>
       <c r="D1002" t="n">
-        <v>24142.88</v>
+        <v>13331.41</v>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B1003" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1003" t="n">
-        <v>610</v>
+        <v>2722</v>
       </c>
       <c r="D1003" t="n">
-        <v>999598.8</v>
+        <v>24142.88</v>
       </c>
     </row>
     <row r="1004">
@@ -16496,42 +16496,42 @@
         <v>46204</v>
       </c>
       <c r="C1004" t="n">
-        <v>2251</v>
+        <v>610</v>
       </c>
       <c r="D1004" t="n">
-        <v>161706.94</v>
+        <v>999598.8</v>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B1005" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1005" t="n">
-        <v>2671</v>
+        <v>2251</v>
       </c>
       <c r="D1005" t="n">
-        <v>77314.24000000001</v>
+        <v>161706.94</v>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B1006" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1006" t="n">
-        <v>89</v>
+        <v>2671</v>
       </c>
       <c r="D1006" t="n">
-        <v>437962.97</v>
+        <v>77314.24000000001</v>
       </c>
     </row>
     <row r="1007">
@@ -16544,10 +16544,10 @@
         <v>46204</v>
       </c>
       <c r="C1007" t="n">
-        <v>2279</v>
+        <v>89</v>
       </c>
       <c r="D1007" t="n">
-        <v>186972.13</v>
+        <v>437962.97</v>
       </c>
     </row>
     <row r="1008">
@@ -16560,154 +16560,154 @@
         <v>46204</v>
       </c>
       <c r="C1008" t="n">
-        <v>477</v>
+        <v>2279</v>
       </c>
       <c r="D1008" t="n">
-        <v>133718.39</v>
+        <v>186972.13</v>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B1009" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1009" t="n">
-        <v>793</v>
+        <v>477</v>
       </c>
       <c r="D1009" t="n">
-        <v>31097.09</v>
+        <v>133718.39</v>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B1010" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1010" t="n">
-        <v>325</v>
+        <v>793</v>
       </c>
       <c r="D1010" t="n">
-        <v>5675.36</v>
+        <v>31097.09</v>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B1011" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1011" t="n">
-        <v>2133</v>
+        <v>325</v>
       </c>
       <c r="D1011" t="n">
-        <v>985974.7</v>
+        <v>5675.36</v>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B1012" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1012" t="n">
-        <v>2695</v>
+        <v>2133</v>
       </c>
       <c r="D1012" t="n">
-        <v>18559.01</v>
+        <v>985974.7</v>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B1013" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1013" t="n">
-        <v>636</v>
+        <v>2695</v>
       </c>
       <c r="D1013" t="n">
-        <v>208605.89</v>
+        <v>18559.01</v>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B1014" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1014" t="n">
-        <v>2541</v>
+        <v>636</v>
       </c>
       <c r="D1014" t="n">
-        <v>264226.93</v>
+        <v>208605.89</v>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B1015" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1015" t="n">
-        <v>1876</v>
+        <v>2541</v>
       </c>
       <c r="D1015" t="n">
-        <v>42316.01</v>
+        <v>264226.93</v>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B1016" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1016" t="n">
-        <v>2211</v>
+        <v>1876</v>
       </c>
       <c r="D1016" t="n">
-        <v>263392.77</v>
+        <v>42316.01</v>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B1017" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1017" t="n">
-        <v>2705</v>
+        <v>2211</v>
       </c>
       <c r="D1017" t="n">
-        <v>213177.94</v>
+        <v>263392.77</v>
       </c>
     </row>
     <row r="1018">
@@ -16720,32 +16720,32 @@
         <v>46204</v>
       </c>
       <c r="C1018" t="n">
-        <v>2341</v>
+        <v>2705</v>
       </c>
       <c r="D1018" t="n">
-        <v>148485.95</v>
+        <v>213177.94</v>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B1019" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1019" t="n">
-        <v>2768</v>
+        <v>2341</v>
       </c>
       <c r="D1019" t="n">
-        <v>50992.55</v>
+        <v>148485.95</v>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B1020" s="2" t="n">
@@ -16755,7 +16755,7 @@
         <v>2768</v>
       </c>
       <c r="D1020" t="n">
-        <v>276158.9</v>
+        <v>50992.55</v>
       </c>
     </row>
     <row r="1021">
@@ -16768,154 +16768,154 @@
         <v>46204</v>
       </c>
       <c r="C1021" t="n">
-        <v>2118</v>
+        <v>2768</v>
       </c>
       <c r="D1021" t="n">
-        <v>264911.7</v>
+        <v>276158.9</v>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B1022" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1022" t="n">
-        <v>2647</v>
+        <v>2118</v>
       </c>
       <c r="D1022" t="n">
-        <v>126332.6</v>
+        <v>264911.7</v>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B1023" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1023" t="n">
-        <v>802</v>
+        <v>2647</v>
       </c>
       <c r="D1023" t="n">
-        <v>73625.37</v>
+        <v>126332.6</v>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B1024" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1024" t="n">
-        <v>1137</v>
+        <v>802</v>
       </c>
       <c r="D1024" t="n">
-        <v>6073.64</v>
+        <v>73625.37</v>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B1025" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1025" t="n">
-        <v>438</v>
+        <v>1137</v>
       </c>
       <c r="D1025" t="n">
-        <v>98947</v>
+        <v>6073.64</v>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B1026" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1026" t="n">
-        <v>952</v>
+        <v>438</v>
       </c>
       <c r="D1026" t="n">
-        <v>125035.84</v>
+        <v>98947</v>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B1027" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1027" t="n">
-        <v>2657</v>
+        <v>952</v>
       </c>
       <c r="D1027" t="n">
-        <v>17271.39</v>
+        <v>125035.84</v>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B1028" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1028" t="n">
-        <v>1327</v>
+        <v>2657</v>
       </c>
       <c r="D1028" t="n">
-        <v>60765.23</v>
+        <v>17271.39</v>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B1029" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1029" t="n">
-        <v>2298</v>
+        <v>1327</v>
       </c>
       <c r="D1029" t="n">
-        <v>27012.83</v>
+        <v>60765.23</v>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B1030" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1030" t="n">
-        <v>2735</v>
+        <v>2298</v>
       </c>
       <c r="D1030" t="n">
-        <v>142926.6</v>
+        <v>27012.83</v>
       </c>
     </row>
     <row r="1031">
@@ -16928,186 +16928,186 @@
         <v>46204</v>
       </c>
       <c r="C1031" t="n">
-        <v>2745</v>
+        <v>2735</v>
       </c>
       <c r="D1031" t="n">
-        <v>159058.42</v>
+        <v>142926.6</v>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B1032" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1032" t="n">
-        <v>2085</v>
+        <v>2745</v>
       </c>
       <c r="D1032" t="n">
-        <v>31584.41</v>
+        <v>159058.42</v>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B1033" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1033" t="n">
-        <v>2685</v>
+        <v>2085</v>
       </c>
       <c r="D1033" t="n">
-        <v>5439.15</v>
+        <v>31584.41</v>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B1034" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1034" t="n">
-        <v>438</v>
+        <v>2685</v>
       </c>
       <c r="D1034" t="n">
-        <v>7941.61</v>
+        <v>5439.15</v>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B1035" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1035" t="n">
-        <v>325</v>
+        <v>438</v>
       </c>
       <c r="D1035" t="n">
-        <v>129.69</v>
+        <v>7941.61</v>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B1036" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1036" t="n">
-        <v>2601</v>
+        <v>325</v>
       </c>
       <c r="D1036" t="n">
-        <v>575524.6</v>
+        <v>129.69</v>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B1037" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1037" t="n">
-        <v>2045</v>
+        <v>2601</v>
       </c>
       <c r="D1037" t="n">
-        <v>428459.54</v>
+        <v>575524.6</v>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B1038" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1038" t="n">
-        <v>2762</v>
+        <v>2045</v>
       </c>
       <c r="D1038" t="n">
-        <v>2511.92</v>
+        <v>428459.54</v>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B1039" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1039" t="n">
-        <v>2706</v>
+        <v>2762</v>
       </c>
       <c r="D1039" t="n">
-        <v>684.9</v>
+        <v>2511.92</v>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B1040" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1040" t="n">
-        <v>2566</v>
+        <v>2706</v>
       </c>
       <c r="D1040" t="n">
-        <v>73066.5</v>
+        <v>684.9</v>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B1041" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1041" t="n">
-        <v>2546</v>
+        <v>2566</v>
       </c>
       <c r="D1041" t="n">
-        <v>7186.53</v>
+        <v>73066.5</v>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B1042" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1042" t="n">
-        <v>749</v>
+        <v>2546</v>
       </c>
       <c r="D1042" t="n">
-        <v>22019.94</v>
+        <v>7186.53</v>
       </c>
     </row>
     <row r="1043">
@@ -17120,42 +17120,42 @@
         <v>46204</v>
       </c>
       <c r="C1043" t="n">
-        <v>2797</v>
+        <v>749</v>
       </c>
       <c r="D1043" t="n">
-        <v>14519.79</v>
+        <v>22019.94</v>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B1044" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1044" t="n">
-        <v>1293</v>
+        <v>2797</v>
       </c>
       <c r="D1044" t="n">
-        <v>1005.13</v>
+        <v>14519.79</v>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B1045" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1045" t="n">
-        <v>1340</v>
+        <v>1293</v>
       </c>
       <c r="D1045" t="n">
-        <v>796.9</v>
+        <v>1005.13</v>
       </c>
     </row>
     <row r="1046">
@@ -17168,42 +17168,42 @@
         <v>46204</v>
       </c>
       <c r="C1046" t="n">
-        <v>2178</v>
+        <v>1340</v>
       </c>
       <c r="D1046" t="n">
-        <v>4662.38</v>
+        <v>796.9</v>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B1047" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1047" t="n">
-        <v>2791</v>
+        <v>2178</v>
       </c>
       <c r="D1047" t="n">
-        <v>71328.67999999999</v>
+        <v>4662.38</v>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B1048" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1048" t="n">
-        <v>2209</v>
+        <v>2791</v>
       </c>
       <c r="D1048" t="n">
-        <v>1492.28</v>
+        <v>71328.67999999999</v>
       </c>
     </row>
     <row r="1049">
@@ -17216,122 +17216,122 @@
         <v>46204</v>
       </c>
       <c r="C1049" t="n">
-        <v>138</v>
+        <v>2209</v>
       </c>
       <c r="D1049" t="n">
-        <v>1725.9</v>
+        <v>1492.28</v>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B1050" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1050" t="n">
-        <v>2792</v>
+        <v>138</v>
       </c>
       <c r="D1050" t="n">
-        <v>4383.83</v>
+        <v>1725.9</v>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B1051" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1051" t="n">
-        <v>2791</v>
+        <v>2792</v>
       </c>
       <c r="D1051" t="n">
-        <v>3222.91</v>
+        <v>4383.83</v>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B1052" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1052" t="n">
-        <v>933</v>
+        <v>2791</v>
       </c>
       <c r="D1052" t="n">
-        <v>-282.99</v>
+        <v>3222.91</v>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B1053" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1053" t="n">
-        <v>630</v>
+        <v>933</v>
       </c>
       <c r="D1053" t="n">
-        <v>45850.67</v>
+        <v>-282.99</v>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B1054" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1054" t="n">
-        <v>1075</v>
+        <v>630</v>
       </c>
       <c r="D1054" t="n">
-        <v>16576.58</v>
+        <v>45850.67</v>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B1055" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1055" t="n">
-        <v>1658</v>
+        <v>1075</v>
       </c>
       <c r="D1055" t="n">
-        <v>696.42</v>
+        <v>16576.58</v>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B1056" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1056" t="n">
-        <v>610</v>
+        <v>1658</v>
       </c>
       <c r="D1056" t="n">
-        <v>0</v>
+        <v>696.42</v>
       </c>
     </row>
     <row r="1057">
@@ -17344,7 +17344,7 @@
         <v>46204</v>
       </c>
       <c r="C1057" t="n">
-        <v>953</v>
+        <v>610</v>
       </c>
       <c r="D1057" t="n">
         <v>0</v>
@@ -17360,7 +17360,7 @@
         <v>46204</v>
       </c>
       <c r="C1058" t="n">
-        <v>477</v>
+        <v>953</v>
       </c>
       <c r="D1058" t="n">
         <v>0</v>
@@ -17369,17 +17369,17 @@
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B1059" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1059" t="n">
-        <v>1518</v>
+        <v>477</v>
       </c>
       <c r="D1059" t="n">
-        <v>2627.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1060">
@@ -17392,74 +17392,74 @@
         <v>46204</v>
       </c>
       <c r="C1060" t="n">
-        <v>1384</v>
+        <v>1518</v>
       </c>
       <c r="D1060" t="n">
-        <v>1301.32</v>
+        <v>2627.98</v>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B1061" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1061" t="n">
-        <v>2667</v>
+        <v>1384</v>
       </c>
       <c r="D1061" t="n">
-        <v>2822.04</v>
+        <v>1301.32</v>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B1062" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1062" t="n">
-        <v>945</v>
+        <v>2667</v>
       </c>
       <c r="D1062" t="n">
-        <v>3418.92</v>
+        <v>2822.04</v>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B1063" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1063" t="n">
-        <v>2539</v>
+        <v>945</v>
       </c>
       <c r="D1063" t="n">
-        <v>906.62</v>
+        <v>3418.92</v>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B1064" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C1064" t="n">
-        <v>1956</v>
+        <v>2539</v>
       </c>
       <c r="D1064" t="n">
-        <v>2024.37</v>
+        <v>906.62</v>
       </c>
     </row>
     <row r="1065">
@@ -17472,10 +17472,10 @@
         <v>46204</v>
       </c>
       <c r="C1065" t="n">
-        <v>2686</v>
+        <v>1956</v>
       </c>
       <c r="D1065" t="n">
-        <v>1171.01</v>
+        <v>2024.37</v>
       </c>
     </row>
     <row r="1066">
@@ -17488,10 +17488,10 @@
         <v>46204</v>
       </c>
       <c r="C1066" t="n">
-        <v>2801</v>
+        <v>2686</v>
       </c>
       <c r="D1066" t="n">
-        <v>2180.84</v>
+        <v>1171.01</v>
       </c>
     </row>
     <row r="1067">
@@ -17504,106 +17504,106 @@
         <v>46204</v>
       </c>
       <c r="C1067" t="n">
-        <v>2639</v>
+        <v>2801</v>
       </c>
       <c r="D1067" t="n">
-        <v>232.83</v>
+        <v>2180.84</v>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B1068" s="2" t="n">
-        <v>46235</v>
+        <v>46204</v>
       </c>
       <c r="C1068" t="n">
-        <v>1890</v>
+        <v>2639</v>
       </c>
       <c r="D1068" t="n">
-        <v>154901.28</v>
+        <v>232.83</v>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B1069" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1069" t="n">
-        <v>1853</v>
+        <v>1890</v>
       </c>
       <c r="D1069" t="n">
-        <v>32009.38</v>
+        <v>154901.28</v>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B1070" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1070" t="n">
-        <v>949</v>
+        <v>1853</v>
       </c>
       <c r="D1070" t="n">
-        <v>87744.64</v>
+        <v>32009.38</v>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B1071" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1071" t="n">
-        <v>2783</v>
+        <v>949</v>
       </c>
       <c r="D1071" t="n">
-        <v>19786.52</v>
+        <v>87744.64</v>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B1072" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1072" t="n">
-        <v>1384</v>
+        <v>2783</v>
       </c>
       <c r="D1072" t="n">
-        <v>198575.15</v>
+        <v>15986.88</v>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B1073" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1073" t="n">
-        <v>1871</v>
+        <v>1384</v>
       </c>
       <c r="D1073" t="n">
-        <v>35816.43</v>
+        <v>198575.15</v>
       </c>
     </row>
     <row r="1074">
@@ -17616,58 +17616,58 @@
         <v>46235</v>
       </c>
       <c r="C1074" t="n">
-        <v>2541</v>
+        <v>1871</v>
       </c>
       <c r="D1074" t="n">
-        <v>44002.07</v>
+        <v>35816.43</v>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B1075" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1075" t="n">
-        <v>40</v>
+        <v>2541</v>
       </c>
       <c r="D1075" t="n">
-        <v>105203.66</v>
+        <v>44002.07</v>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B1076" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1076" t="n">
-        <v>2359</v>
+        <v>40</v>
       </c>
       <c r="D1076" t="n">
-        <v>44540.83</v>
+        <v>106317.23</v>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B1077" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1077" t="n">
-        <v>2659</v>
+        <v>2359</v>
       </c>
       <c r="D1077" t="n">
-        <v>94404.37</v>
+        <v>44540.83</v>
       </c>
     </row>
     <row r="1078">
@@ -17680,138 +17680,138 @@
         <v>46235</v>
       </c>
       <c r="C1078" t="n">
-        <v>794</v>
+        <v>2659</v>
       </c>
       <c r="D1078" t="n">
-        <v>409.05</v>
+        <v>94404.37</v>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B1079" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1079" t="n">
-        <v>1108</v>
+        <v>794</v>
       </c>
       <c r="D1079" t="n">
-        <v>88400.28</v>
+        <v>409.05</v>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B1080" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1080" t="n">
-        <v>1364</v>
+        <v>1108</v>
       </c>
       <c r="D1080" t="n">
-        <v>2048.59</v>
+        <v>88400.28</v>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B1081" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1081" t="n">
-        <v>326</v>
+        <v>1364</v>
       </c>
       <c r="D1081" t="n">
-        <v>33.16</v>
+        <v>2048.59</v>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B1082" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1082" t="n">
-        <v>1293</v>
+        <v>326</v>
       </c>
       <c r="D1082" t="n">
-        <v>222508.83</v>
+        <v>33.16</v>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B1083" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1083" t="n">
-        <v>285</v>
+        <v>1293</v>
       </c>
       <c r="D1083" t="n">
-        <v>154178.28</v>
+        <v>222508.83</v>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B1084" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1084" t="n">
-        <v>2709</v>
+        <v>285</v>
       </c>
       <c r="D1084" t="n">
-        <v>59326.58</v>
+        <v>154178.28</v>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B1085" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1085" t="n">
-        <v>1380</v>
+        <v>2709</v>
       </c>
       <c r="D1085" t="n">
-        <v>296.16</v>
+        <v>59326.58</v>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B1086" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1086" t="n">
-        <v>1690</v>
+        <v>1380</v>
       </c>
       <c r="D1086" t="n">
-        <v>11390.73</v>
+        <v>296.16</v>
       </c>
     </row>
     <row r="1087">
@@ -17824,186 +17824,186 @@
         <v>46235</v>
       </c>
       <c r="C1087" t="n">
-        <v>1304</v>
+        <v>1690</v>
       </c>
       <c r="D1087" t="n">
-        <v>36116.69</v>
+        <v>11390.73</v>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B1088" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1088" t="n">
-        <v>949</v>
+        <v>1304</v>
       </c>
       <c r="D1088" t="n">
-        <v>15000</v>
+        <v>36116.69</v>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B1089" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1089" t="n">
-        <v>2737</v>
+        <v>949</v>
       </c>
       <c r="D1089" t="n">
-        <v>40726.87</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B1090" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1090" t="n">
-        <v>2107</v>
+        <v>2737</v>
       </c>
       <c r="D1090" t="n">
-        <v>132140.59</v>
+        <v>40726.87</v>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B1091" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1091" t="n">
-        <v>793</v>
+        <v>2107</v>
       </c>
       <c r="D1091" t="n">
-        <v>5058.45</v>
+        <v>132140.59</v>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B1092" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1092" t="n">
-        <v>2728</v>
+        <v>793</v>
       </c>
       <c r="D1092" t="n">
-        <v>51338.52</v>
+        <v>5058.45</v>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B1093" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1093" t="n">
-        <v>2820</v>
+        <v>2728</v>
       </c>
       <c r="D1093" t="n">
-        <v>1412.94</v>
+        <v>51338.52</v>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B1094" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1094" t="n">
-        <v>2657</v>
+        <v>2820</v>
       </c>
       <c r="D1094" t="n">
-        <v>37203.05</v>
+        <v>1412.94</v>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B1095" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1095" t="n">
-        <v>1456</v>
+        <v>2657</v>
       </c>
       <c r="D1095" t="n">
-        <v>52001.75</v>
+        <v>37203.05</v>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B1096" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1096" t="n">
-        <v>2580</v>
+        <v>1456</v>
       </c>
       <c r="D1096" t="n">
-        <v>3978.49</v>
+        <v>51931.69</v>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B1097" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1097" t="n">
-        <v>374</v>
+        <v>2580</v>
       </c>
       <c r="D1097" t="n">
-        <v>99.76000000000001</v>
+        <v>3978.49</v>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B1098" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1098" t="n">
-        <v>2639</v>
+        <v>374</v>
       </c>
       <c r="D1098" t="n">
-        <v>21058</v>
+        <v>99.76000000000001</v>
       </c>
     </row>
     <row r="1099">
@@ -18016,42 +18016,42 @@
         <v>46235</v>
       </c>
       <c r="C1099" t="n">
-        <v>1840</v>
+        <v>2639</v>
       </c>
       <c r="D1099" t="n">
-        <v>1506.67</v>
+        <v>21058</v>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B1100" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1100" t="n">
-        <v>2678</v>
+        <v>1840</v>
       </c>
       <c r="D1100" t="n">
-        <v>5305.71</v>
+        <v>1506.67</v>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B1101" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1101" t="n">
-        <v>1465</v>
+        <v>2678</v>
       </c>
       <c r="D1101" t="n">
-        <v>1191.05</v>
+        <v>5305.71</v>
       </c>
     </row>
     <row r="1102">
@@ -18064,10 +18064,10 @@
         <v>46235</v>
       </c>
       <c r="C1102" t="n">
-        <v>2433</v>
+        <v>1465</v>
       </c>
       <c r="D1102" t="n">
-        <v>-272.59</v>
+        <v>1191.05</v>
       </c>
     </row>
     <row r="1103">
@@ -18080,10 +18080,10 @@
         <v>46235</v>
       </c>
       <c r="C1103" t="n">
-        <v>1327</v>
+        <v>2433</v>
       </c>
       <c r="D1103" t="n">
-        <v>29350.66</v>
+        <v>-272.59</v>
       </c>
     </row>
     <row r="1104">
@@ -18096,10 +18096,10 @@
         <v>46235</v>
       </c>
       <c r="C1104" t="n">
-        <v>14</v>
+        <v>1327</v>
       </c>
       <c r="D1104" t="n">
-        <v>141640.16</v>
+        <v>29350.66</v>
       </c>
     </row>
     <row r="1105">
@@ -18112,10 +18112,10 @@
         <v>46235</v>
       </c>
       <c r="C1105" t="n">
-        <v>483</v>
+        <v>14</v>
       </c>
       <c r="D1105" t="n">
-        <v>2074.19</v>
+        <v>141640.16</v>
       </c>
     </row>
     <row r="1106">
@@ -18128,234 +18128,234 @@
         <v>46235</v>
       </c>
       <c r="C1106" t="n">
-        <v>1756</v>
+        <v>483</v>
       </c>
       <c r="D1106" t="n">
-        <v>3668.02</v>
+        <v>2074.19</v>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B1107" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1107" t="n">
-        <v>2706</v>
+        <v>1756</v>
       </c>
       <c r="D1107" t="n">
-        <v>1074.08</v>
+        <v>3668.02</v>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B1108" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1108" t="n">
-        <v>766</v>
+        <v>2706</v>
       </c>
       <c r="D1108" t="n">
-        <v>890.0700000000001</v>
+        <v>1074.08</v>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B1109" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1109" t="n">
-        <v>2719</v>
+        <v>766</v>
       </c>
       <c r="D1109" t="n">
-        <v>349.39</v>
+        <v>890.0700000000001</v>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B1110" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1110" t="n">
-        <v>20</v>
+        <v>2719</v>
       </c>
       <c r="D1110" t="n">
-        <v>24720.14</v>
+        <v>349.39</v>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B1111" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1111" t="n">
-        <v>2819</v>
+        <v>20</v>
       </c>
       <c r="D1111" t="n">
-        <v>10743.88</v>
+        <v>24720.14</v>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B1112" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1112" t="n">
-        <v>2777</v>
+        <v>2819</v>
       </c>
       <c r="D1112" t="n">
-        <v>2398.49</v>
+        <v>10743.88</v>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B1113" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1113" t="n">
-        <v>138</v>
+        <v>2777</v>
       </c>
       <c r="D1113" t="n">
-        <v>742.35</v>
+        <v>2398.49</v>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B1114" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1114" t="n">
-        <v>2585</v>
+        <v>138</v>
       </c>
       <c r="D1114" t="n">
-        <v>1594.6</v>
+        <v>742.35</v>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B1115" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1115" t="n">
-        <v>326</v>
+        <v>2585</v>
       </c>
       <c r="D1115" t="n">
-        <v>5491.22</v>
+        <v>1594.6</v>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B1116" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1116" t="n">
-        <v>2755</v>
+        <v>326</v>
       </c>
       <c r="D1116" t="n">
-        <v>1434.78</v>
+        <v>5491.22</v>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B1117" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1117" t="n">
-        <v>2815</v>
+        <v>2755</v>
       </c>
       <c r="D1117" t="n">
-        <v>38197.02</v>
+        <v>1434.78</v>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B1118" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1118" t="n">
-        <v>2627</v>
+        <v>2815</v>
       </c>
       <c r="D1118" t="n">
-        <v>-279.71</v>
+        <v>38197.02</v>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B1119" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1119" t="n">
-        <v>522</v>
+        <v>2627</v>
       </c>
       <c r="D1119" t="n">
-        <v>2410.32</v>
+        <v>-279.71</v>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B1120" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1120" t="n">
-        <v>559</v>
+        <v>522</v>
       </c>
       <c r="D1120" t="n">
-        <v>1151.07</v>
+        <v>2410.32</v>
       </c>
     </row>
     <row r="1121">
@@ -18368,121 +18368,137 @@
         <v>46235</v>
       </c>
       <c r="C1121" t="n">
-        <v>451</v>
+        <v>559</v>
       </c>
       <c r="D1121" t="n">
-        <v>659.9400000000001</v>
+        <v>1151.07</v>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B1122" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1122" t="n">
-        <v>6564</v>
+        <v>451</v>
       </c>
       <c r="D1122" t="n">
-        <v>21488.24</v>
+        <v>659.9400000000001</v>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B1123" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1123" t="n">
-        <v>1115</v>
+        <v>6564</v>
       </c>
       <c r="D1123" t="n">
-        <v>2421.04</v>
+        <v>21488.24</v>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B1124" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1124" t="n">
-        <v>2449</v>
+        <v>1115</v>
       </c>
       <c r="D1124" t="n">
-        <v>1427.04</v>
+        <v>2421.04</v>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B1125" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1125" t="n">
-        <v>2310</v>
+        <v>2449</v>
       </c>
       <c r="D1125" t="n">
-        <v>2670.63</v>
+        <v>1427.04</v>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B1126" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1126" t="n">
-        <v>2688</v>
+        <v>2310</v>
       </c>
       <c r="D1126" t="n">
-        <v>373.44</v>
+        <v>2670.63</v>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B1127" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C1127" t="n">
-        <v>1653</v>
+        <v>2688</v>
       </c>
       <c r="D1127" t="n">
-        <v>328.76</v>
+        <v>373.44</v>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B1128" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C1128" t="n">
+        <v>1653</v>
+      </c>
+      <c r="D1128" t="n">
+        <v>328.76</v>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B1128" s="2" t="n">
-        <v>46235</v>
-      </c>
-      <c r="C1128" t="n">
+      <c r="B1129" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C1129" t="n">
         <v>325</v>
       </c>
-      <c r="D1128" t="n">
+      <c r="D1129" t="n">
         <v>145.62</v>
       </c>
     </row>

--- a/data/faturamento_realizado.xlsx
+++ b/data/faturamento_realizado.xlsx
@@ -6195,7 +6195,7 @@
         <v>326</v>
       </c>
       <c r="D360" t="n">
-        <v>42942.24</v>
+        <v>43580.66</v>
       </c>
     </row>
     <row r="361">
@@ -10547,7 +10547,7 @@
         <v>42</v>
       </c>
       <c r="D632" t="n">
-        <v>435426.76</v>
+        <v>436132.48</v>
       </c>
     </row>
     <row r="633">
@@ -12755,7 +12755,7 @@
         <v>341</v>
       </c>
       <c r="D770" t="n">
-        <v>6252.69</v>
+        <v>6886.19</v>
       </c>
     </row>
     <row r="771">
@@ -12851,7 +12851,7 @@
         <v>1465</v>
       </c>
       <c r="D776" t="n">
-        <v>155103.66</v>
+        <v>156209.03</v>
       </c>
     </row>
     <row r="777">
@@ -15123,7 +15123,7 @@
         <v>1810</v>
       </c>
       <c r="D918" t="n">
-        <v>13596.67</v>
+        <v>16782.77</v>
       </c>
     </row>
     <row r="919">
@@ -17651,7 +17651,7 @@
         <v>40</v>
       </c>
       <c r="D1076" t="n">
-        <v>106317.23</v>
+        <v>106759.96</v>
       </c>
     </row>
     <row r="1077">

--- a/data/faturamento_realizado.xlsx
+++ b/data/faturamento_realizado.xlsx
@@ -450,7 +450,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>COD_TELENVENDA</t>
+          <t>COD_TELEVENDA</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
